--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484138_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484138_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. DE LEON</t>
+          <t>A. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3017</v>
+        <v>2.9955</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3668</v>
+        <v>6.1253</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.065</v>
+        <v>-3.1298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9348</v>
+        <v>-1.0308</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1899</v>
+        <v>3.2509</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2551</v>
+        <v>-4.2817</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5759</v>
+        <v>4.6297</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4554</v>
+        <v>5.1868</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1205</v>
+        <v>-0.5572</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6411</v>
+        <v>-5.6605</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2655</v>
+        <v>-1.9359</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3756</v>
+        <v>-3.7246</v>
       </c>
       <c r="P2" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-0.1984</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-1.1903</v>
-      </c>
       <c r="R2" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1685</v>
+        <v>0.8361</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7152</v>
+        <v>0.4876</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4534</v>
+        <v>0.3485</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="W2" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. POU BLINNIKOV</t>
+          <t>R. DE LEON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1015</v>
+        <v>1.5276</v>
       </c>
       <c r="E3" t="n">
-        <v>6.063</v>
+        <v>2.5926</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9614</v>
+        <v>-1.065</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0308</v>
+        <v>0.9348</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2509</v>
+        <v>1.1899</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.2817</v>
+        <v>-0.2551</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6297</v>
+        <v>2.5759</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1868</v>
+        <v>2.4554</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5572</v>
+        <v>0.1205</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.6605</v>
+        <v>-1.6411</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9359</v>
+        <v>-1.2655</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.7246</v>
+        <v>-0.3756</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.3944</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4252</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5168</v>
+        <v>0.4534</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2065</v>
+        <v>-0.6032</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.4476</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6759</v>
+        <v>3.8006</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.0444</v>
+        <v>-3.353</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7432</v>
@@ -766,13 +766,13 @@
         <v>3.5709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7635</v>
+        <v>0.5796</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0112</v>
+        <v>0.1135</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.4661</v>
       </c>
       <c r="V4" t="n">
         <v>1.2065</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MARTINEZ JANER</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2108</v>
+        <v>-0.0181</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1623</v>
+        <v>0.5282</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0485</v>
+        <v>-0.5463</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3032</v>
+        <v>0.0258</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5442</v>
+        <v>-0.2774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.241</v>
+        <v>0.3032</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0376</v>
+        <v>1.4865</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6802</v>
+        <v>0.121</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6425999999999999</v>
+        <v>1.3655</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2656</v>
+        <v>-1.4607</v>
       </c>
       <c r="N5" t="n">
-        <v>0.136</v>
+        <v>-0.3983</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4016</v>
+        <v>-1.0623</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.106</v>
+        <v>-0.5002</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1247</v>
+        <v>-0.2324</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0187</v>
+        <v>-0.2678</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>B. MARTINEZ JANER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3063</v>
+        <v>-0.1827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3241</v>
+        <v>-0.1623</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6304</v>
+        <v>-0.0204</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0258</v>
+        <v>-0.3032</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2774</v>
+        <v>-0.5442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3032</v>
+        <v>0.241</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4865</v>
+        <v>-0.0376</v>
       </c>
       <c r="K6" t="n">
-        <v>0.121</v>
+        <v>-0.6802</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3655</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4607</v>
+        <v>-0.2656</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3983</v>
+        <v>0.136</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0623</v>
+        <v>-0.4016</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7884</v>
+        <v>-0.0779</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4364</v>
+        <v>-0.1247</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.352</v>
+        <v>0.0468</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6401</v>
+        <v>-1.3872</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8246</v>
+        <v>3.3677</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8155</v>
+        <v>-4.7549</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4043</v>
+        <v>-3.3099</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4535</v>
+        <v>-1.6231</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0492</v>
+        <v>-1.6868</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5956</v>
+        <v>1.7718</v>
       </c>
       <c r="K7" t="n">
-        <v>0.348</v>
+        <v>0.5242</v>
       </c>
       <c r="L7" t="n">
         <v>1.2476</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9999</v>
+        <v>-5.0817</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8016</v>
+        <v>-2.1473</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1983</v>
+        <v>-2.9343</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4342</v>
+        <v>-0.2125</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4364</v>
+        <v>-0.357</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0022</v>
+        <v>0.1445</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6032</v>
+        <v>1.7384</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.9449</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7749</v>
+        <v>-1.5318</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5562</v>
+        <v>-0.6603</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.331</v>
+        <v>-0.8716</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1525</v>
+        <v>-0.4043</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.761</v>
+        <v>-0.4535</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3915</v>
+        <v>0.0492</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1015</v>
+        <v>1.5956</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4421</v>
+        <v>0.348</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6594</v>
+        <v>1.2476</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.254</v>
+        <v>-1.9999</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2031</v>
+        <v>-0.8016</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.0509</v>
+        <v>-1.1983</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1741</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7774</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1712</v>
+        <v>-0.3259</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3629</v>
+        <v>-0.272</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1917</v>
+        <v>-0.0539</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6032</v>
+        <v>-0.6032</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3373</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8843</v>
+        <v>-1.7023</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0389</v>
+        <v>0.5165</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.9233</v>
+        <v>-2.2188</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3099</v>
+        <v>-2.1525</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6231</v>
+        <v>-0.761</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6868</v>
+        <v>-1.3915</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7718</v>
+        <v>3.1015</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5242</v>
+        <v>1.4421</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2476</v>
+        <v>1.6594</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.0817</v>
+        <v>-5.254</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1473</v>
+        <v>-2.2031</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.9343</v>
+        <v>-3.0509</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3887</v>
+        <v>2.7774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7096</v>
+        <v>0.2437</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6858</v>
+        <v>0.3232</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0238</v>
+        <v>-0.0794</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7384</v>
+        <v>0.6032</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9449</v>
+        <v>0.266</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0309</v>
+        <v>-3.039</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2191</v>
+        <v>-0.8287</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1882</v>
+        <v>-2.2103</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3315</v>
+        <v>-4.1103</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6227</v>
+        <v>0.9631</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7088</v>
+        <v>-5.0734</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.479</v>
+        <v>0.3389</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1588</v>
+        <v>2.899</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3202</v>
+        <v>-2.5601</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8525</v>
+        <v>-4.4492</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4639</v>
+        <v>-1.9359</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3886</v>
+        <v>-2.5132</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0799</v>
+        <v>0.2778</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7481</v>
+        <v>0.0228</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6682</v>
+        <v>0.255</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4583</v>
+        <v>-3.7568</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9113</v>
+        <v>-3.7486</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.547</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1103</v>
+        <v>-3.3315</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9631</v>
+        <v>-1.6227</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.0734</v>
+        <v>-1.7088</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3389</v>
+        <v>-2.479</v>
       </c>
       <c r="K11" t="n">
-        <v>2.899</v>
+        <v>-1.1588</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5601</v>
+        <v>-1.3202</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.4492</v>
+        <v>-0.8525</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9359</v>
+        <v>-0.4639</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5132</v>
+        <v>-0.3886</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1415</v>
+        <v>0.1941</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0599</v>
+        <v>-0.2777</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.4718</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2708</v>
+        <v>-6.647200000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9076</v>
+        <v>11.531</v>
       </c>
       <c r="F12" t="n">
         <v>-18.1783</v>
@@ -1369,7 +1369,7 @@
         <v>15.3268</v>
       </c>
       <c r="L12" t="n">
-        <v>2.493400000000001</v>
+        <v>2.493399999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-32.2455</v>
@@ -1390,13 +1390,13 @@
         <v>18.8465</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7856</v>
+        <v>2.4092</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0007999999999996898</v>
+        <v>0.6242999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7848</v>
+        <v>1.785</v>
       </c>
       <c r="V12" t="n">
         <v>1.4012</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9315</v>
+        <v>5.3397</v>
       </c>
       <c r="E13" t="n">
-        <v>7.018</v>
+        <v>7.4261</v>
       </c>
       <c r="F13" t="n">
         <v>-2.0864</v>
@@ -1468,10 +1468,10 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9523</v>
+        <v>-0.5442</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8615</v>
+        <v>-0.4534</v>
       </c>
       <c r="U13" t="n">
         <v>-0.09080000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0502</v>
+        <v>4.0604</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8448</v>
+        <v>4.7428</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7946</v>
+        <v>-0.6824</v>
       </c>
       <c r="G14" t="n">
         <v>3.6329</v>
@@ -1546,13 +1546,13 @@
         <v>2.3806</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5827</v>
+        <v>-0.5725</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1813</v>
+        <v>-0.2833</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4014</v>
+        <v>-0.2892</v>
       </c>
       <c r="V14" t="n">
         <v>0.6032</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3608</v>
+        <v>3.9653</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0337</v>
+        <v>5.4418</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6729</v>
+        <v>-1.4765</v>
       </c>
       <c r="G15" t="n">
         <v>7.2218</v>
@@ -1624,13 +1624,13 @@
         <v>2.3806</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4561</v>
+        <v>-0.8516</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9125</v>
+        <v>-0.5044</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5437</v>
+        <v>-0.3473</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8097</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>J. MIRANDA VARGAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3964</v>
+        <v>1.4457</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5561</v>
+        <v>0.5845</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8403</v>
+        <v>0.8612</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7178</v>
+        <v>3.8437</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1812</v>
+        <v>0.9119</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5366</v>
+        <v>2.9318</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8803</v>
+        <v>4.0226</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9139</v>
+        <v>0.9678</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9664</v>
+        <v>3.0548</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1625</v>
+        <v>-0.1788</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.7326</v>
+        <v>-0.0558</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5702</v>
+        <v>-0.123</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5952</v>
+        <v>-3.3725</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9758</v>
+        <v>-3.9677</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3806</v>
+        <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0078</v>
+        <v>0.3712</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3856</v>
+        <v>-0.0737</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6222</v>
+        <v>0.4449</v>
       </c>
       <c r="V16" t="n">
-        <v>0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MIRANDA VARGAS</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.512</v>
+        <v>1.3915</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4825</v>
+        <v>0.9439</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0295</v>
+        <v>0.4476</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8437</v>
+        <v>1.7178</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9119</v>
+        <v>0.1812</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9318</v>
+        <v>1.5366</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0226</v>
+        <v>3.8803</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9678</v>
+        <v>2.9139</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0548</v>
+        <v>0.9664</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1788</v>
+        <v>-2.1625</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0558</v>
+        <v>-2.7326</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.123</v>
+        <v>0.5702</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.3725</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9677</v>
+        <v>-2.9758</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5952</v>
+        <v>2.3806</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4375</v>
+        <v>0.0028</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1757</v>
+        <v>-0.2266</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6132</v>
+        <v>0.2294</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9815</v>
+        <v>0.9177</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9874</v>
+        <v>1.7834</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.006</v>
+        <v>-0.8657</v>
       </c>
       <c r="G18" t="n">
         <v>0.08790000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>0.513</v>
+        <v>0.4492</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5159</v>
+        <v>0.3118</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0029</v>
+        <v>0.1374</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2065</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9275</v>
+        <v>-1.7974</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6741</v>
+        <v>-1.5721</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2533</v>
+        <v>-0.2253</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0166</v>
@@ -1936,13 +1936,13 @@
         <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1173</v>
+        <v>0.0127</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.055</v>
+        <v>-0.0269</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5044</v>
+        <v>-2.3463</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4335</v>
+        <v>-0.3314</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0709</v>
+        <v>-2.0148</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5775</v>
@@ -2014,13 +2014,13 @@
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1723</v>
+        <v>-0.0142</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1757</v>
+        <v>-0.0737</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0034</v>
+        <v>0.0595</v>
       </c>
       <c r="V20" t="n">
         <v>-2.3417</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6512</v>
+        <v>-2.7354</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2073</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4439</v>
+        <v>-1.5281</v>
       </c>
       <c r="G21" t="n">
         <v>0.0964</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0459</v>
+        <v>-0.0383</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3576</v>
+        <v>0.2734</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8785</v>
+        <v>-2.9703</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5708</v>
+        <v>0.3668</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4493</v>
+        <v>-3.3371</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1035</v>
@@ -2170,13 +2170,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.509</v>
+        <v>-0.6008</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0056</v>
+        <v>-0.2097</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5034</v>
+        <v>-0.3912</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8692</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.2708</v>
+        <v>7.270899999999997</v>
       </c>
       <c r="E23" t="n">
-        <v>18.1784</v>
+        <v>18.1785</v>
       </c>
       <c r="F23" t="n">
         <v>-10.9075</v>
@@ -2248,13 +2248,13 @@
         <v>14.879</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7855</v>
+        <v>-1.7857</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.7848</v>
+        <v>-1.785</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0008000000000000229</v>
+        <v>-0.0007999999999999674</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4013</v>
